--- a/demo_project_2/team-kapazitaet.xlsx
+++ b/demo_project_2/team-kapazitaet.xlsx
@@ -900,13 +900,13 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>40</v>
       </c>
       <c r="E5">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="F5" t="s">
         <v>22</v>
